--- a/server/assets/monthly-financial-report-template.xlsx
+++ b/server/assets/monthly-financial-report-template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度结算" sheetId="1" r:id="R1e28a184e1d04ac8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="手工项目明细" sheetId="2" r:id="Rbb8cc0c7c1ed4a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动来源明细" sheetId="3" r:id="Rfc9cdd250fd04dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="4" r:id="Rb055eb375bff4bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度结算" sheetId="1" r:id="Re6520feb0fa34728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="手工项目明细" sheetId="2" r:id="R4c6104f3ebd74408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动来源明细" sheetId="3" r:id="Raa647e6ac09a4d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="4" r:id="R6892232b43564264"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +99,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -152,6 +152,13 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -821,30 +828,32 @@
         <x:v>福利金汇总</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>账户一总额</x:v>
+        <x:v>账户一</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>407费用</x:v>
+        <x:v>饮用水</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
+        <x:v>办公</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>电费</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
         <x:v>407-AI</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="G22" s="14" t="str">
         <x:v>8H-AI</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
-        <x:v>账户一补充收入</x:v>
-      </x:c>
-      <x:c r="G22" s="14"/>
-      <x:c r="H22" s="14"/>
+      <x:c r="H22" s="14" t="str"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="13" t="n">
-        <x:f>ROUND(SUM(C23:E23)+SUM(C25:E25),2)</x:f>
+        <x:f>ROUND(B23+B25,2)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="B23" s="13" t="n">
-        <x:f>ROUND(SUM(C23:E23),2)</x:f>
+        <x:f>ROUND(SUM(C23:G23),2)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C23" s="13" t="n">
@@ -859,15 +868,17 @@
       <x:c r="F23" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="12"/>
-      <x:c r="H23" s="12"/>
+      <x:c r="G23" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="15" t="str">
-        <x:v>福利金汇总</x:v>
-      </x:c>
+      <x:c r="A24" s="15" t="str"/>
       <x:c r="B24" s="15" t="str">
-        <x:v>账户二总额</x:v>
+        <x:v>账户二</x:v>
       </x:c>
       <x:c r="C24" s="15" t="str">
         <x:v>茶歇</x:v>
@@ -878,14 +889,12 @@
       <x:c r="E24" s="15" t="str">
         <x:v>体检</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str">
-        <x:v>账户二补充收入</x:v>
-      </x:c>
-      <x:c r="G24" s="14"/>
-      <x:c r="H24" s="14"/>
+      <x:c r="F24" s="15" t="str"/>
+      <x:c r="G24" s="14" t="str"/>
+      <x:c r="H24" s="14" t="str"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="13"/>
+      <x:c r="A25" s="13" t="str"/>
       <x:c r="B25" s="13" t="n">
         <x:f>ROUND(SUM(C25:E25),2)</x:f>
         <x:v>0</x:v>
@@ -899,11 +908,9 @@
       <x:c r="E25" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="12"/>
-      <x:c r="H25" s="12"/>
+      <x:c r="F25" s="13" t="str"/>
+      <x:c r="G25" s="13" t="str"/>
+      <x:c r="H25" s="13" t="str"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="3"/>
@@ -946,9 +953,9 @@
         <x:v>团队可支配</x:v>
       </x:c>
       <x:c r="B28" s="14"/>
-      <x:c r="C28" s="15" t="n">
+      <x:c r="C28" s="15" t="e">
         <x:f>ROUND(B29+E29+G31+G32,2)</x:f>
-        <x:v>0</x:v>
+        <x:v>#VALUE!</x:v>
       </x:c>
       <x:c r="D28" s="14"/>
       <x:c r="E28" s="14"/>
@@ -956,70 +963,65 @@
       <x:c r="G28" s="14"/>
       <x:c r="H28" s="14"/>
     </x:row>
-    <x:row r="29" ht="24" customHeight="1">
+    <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="14" t="str">
         <x:v>一般-总额</x:v>
       </x:c>
-      <x:c r="B29" s="15" t="n">
-        <x:f>ROUND(A7+F11+G11-D15-E15-F15-H15-A17,2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="14"/>
-      <x:c r="D29" s="14" t="str">
+      <x:c r="B29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
         <x:v>商务-总额</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="n">
-        <x:f>ROUND(C7+D11+E11+H11-G15-A19,2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="str">
+      <x:c r="D29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
         <x:v>福利金-总额</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="n">
-        <x:f>ROUND(G31+G32,2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="14"/>
-    </x:row>
-    <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="12"/>
-      <x:c r="B30" s="12"/>
-      <x:c r="C30" s="12"/>
-      <x:c r="D30" s="12"/>
-      <x:c r="E30" s="12"/>
-      <x:c r="F30" s="12"/>
-      <x:c r="G30" s="12"/>
-      <x:c r="H30" s="12"/>
+      <x:c r="F29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>账户一-总额</x:v>
+      </x:c>
+      <x:c r="H29" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="30" customHeight="1">
+      <x:c r="A30" s="14" t="str"/>
+      <x:c r="B30" s="13" t="str"/>
+      <x:c r="C30" s="14" t="str"/>
+      <x:c r="D30" s="13" t="str"/>
+      <x:c r="E30" s="14" t="str"/>
+      <x:c r="F30" s="13" t="str"/>
+      <x:c r="G30" s="14" t="str">
+        <x:v>账户二-总额</x:v>
+      </x:c>
+      <x:c r="H30" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="12"/>
-      <x:c r="B31" s="12"/>
-      <x:c r="C31" s="12"/>
-      <x:c r="D31" s="12"/>
-      <x:c r="E31" s="12"/>
-      <x:c r="F31" s="14" t="str">
-        <x:v>账户一-总额</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="n">
-        <x:f>ROUND(G7+F23-C23-D23-E23,2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H31" s="14"/>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="12"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="12"/>
-      <x:c r="E32" s="12"/>
-      <x:c r="F32" s="14" t="str">
-        <x:v>账户二-总额</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="n">
-        <x:f>ROUND(H7+F25-C25-D25-E25,2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="14"/>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1041,18 +1043,16 @@
     <x:mergeCell ref="A10:B10"/>
     <x:mergeCell ref="A11:B11"/>
     <x:mergeCell ref="A14:A15"/>
-    <x:mergeCell ref="F22:H22"/>
-    <x:mergeCell ref="F23:H23"/>
-    <x:mergeCell ref="F24:H24"/>
-    <x:mergeCell ref="F25:H25"/>
     <x:mergeCell ref="A28:B28"/>
     <x:mergeCell ref="C28:H28"/>
-    <x:mergeCell ref="B29:C30"/>
+    <x:mergeCell ref="B14:C15"/>
+    <x:mergeCell ref="A23:A25"/>
+    <x:mergeCell ref="A29:A30"/>
+    <x:mergeCell ref="B29:B30"/>
+    <x:mergeCell ref="C29:C30"/>
+    <x:mergeCell ref="D29:D30"/>
     <x:mergeCell ref="E29:E30"/>
-    <x:mergeCell ref="G29:H30"/>
-    <x:mergeCell ref="G31:H31"/>
-    <x:mergeCell ref="G32:H32"/>
-    <x:mergeCell ref="B14:C15"/>
+    <x:mergeCell ref="F29:F30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
